--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488064_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488064_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.472</v>
+        <v>6.6841</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7487</v>
+        <v>6.0169</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.6672</v>
       </c>
       <c r="G2" t="n">
         <v>2.0738</v>
@@ -610,13 +610,13 @@
         <v>3.3698</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2356</v>
+        <v>2.4476</v>
       </c>
       <c r="T2" t="n">
-        <v>4.4237</v>
+        <v>2.6919</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1881</v>
+        <v>-0.2442</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2071</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0506</v>
+        <v>5.4758</v>
       </c>
       <c r="E3" t="n">
-        <v>2.768</v>
+        <v>4.0528</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2826</v>
+        <v>1.423</v>
       </c>
       <c r="G3" t="n">
         <v>6.081</v>
@@ -688,13 +688,13 @@
         <v>2.7751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5745</v>
+        <v>0.8507</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7157</v>
+        <v>0.5692</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1412</v>
+        <v>0.2816</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2666</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. DIKE EGUN</t>
+          <t>O. ZARACHO PAEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7661</v>
+        <v>1.8799</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9725</v>
+        <v>1.7107</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7936</v>
+        <v>0.1692</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2232</v>
+        <v>0.6175</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5861</v>
+        <v>-0.031</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8093</v>
+        <v>0.6485</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6752</v>
+        <v>1.3491</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7996</v>
+        <v>0.7062</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1244</v>
+        <v>0.6428</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8984</v>
+        <v>-0.7315</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2136</v>
+        <v>-0.7372</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6848</v>
+        <v>0.0057</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4151</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1057</v>
+        <v>0.3616</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6906</v>
+        <v>0.1762</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0704</v>
+        <v>-0.2666</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6036</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>P. LÓPEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9989</v>
+        <v>1.8133</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7232</v>
+        <v>1.8133</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2757</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1117</v>
+        <v>1.8133</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1063</v>
+        <v>1.2107</v>
       </c>
       <c r="I5" t="n">
-        <v>0.218</v>
+        <v>0.6027</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4903</v>
+        <v>1.8133</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2894</v>
+        <v>1.2107</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2009</v>
+        <v>0.6027</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3786</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3957</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0171</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.352</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.017</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.335</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. LÓPEZ GÓMEZ</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8133</v>
+        <v>1.5343</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8133</v>
+        <v>1.1744</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.3599</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8133</v>
+        <v>0.1117</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2107</v>
+        <v>-0.1063</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6027</v>
+        <v>0.218</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8133</v>
+        <v>0.4903</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2107</v>
+        <v>0.2894</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6027</v>
+        <v>0.2009</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.3786</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.3957</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.0171</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.8874</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.4682</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.4193</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. ZARACHO PAEZ</t>
+          <t>K. DIKE EGUN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6761</v>
+        <v>1.1705</v>
       </c>
       <c r="E7" t="n">
-        <v>1.507</v>
+        <v>0.405</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1692</v>
+        <v>0.7655</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6175</v>
+        <v>0.2232</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.031</v>
+        <v>-0.5861</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6485</v>
+        <v>0.8093</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3491</v>
+        <v>-0.6752</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7062</v>
+        <v>-0.7996</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6428</v>
+        <v>0.1244</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7315</v>
+        <v>0.8984</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7372</v>
+        <v>0.2136</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0057</v>
+        <v>0.6848</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9911</v>
+        <v>0.1982</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S7" t="n">
-        <v>0.334</v>
+        <v>0.8195</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1579</v>
+        <v>1.5382</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1762</v>
+        <v>-0.7187</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2666</v>
+        <v>-0.0704</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2666</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. LASCORZ RIVARES</t>
+          <t>A. BUZZO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.22</v>
+        <v>0.2948</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2963</v>
+        <v>-0.4497</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5163</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5819</v>
+        <v>-4.0661</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0876</v>
+        <v>-3.9399</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6695</v>
+        <v>-0.1262</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1609</v>
+        <v>-1.8134</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0404</v>
+        <v>-1.2626</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1205</v>
+        <v>-0.5508</v>
       </c>
       <c r="M9" t="n">
-        <v>0.421</v>
+        <v>-2.2527</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.128</v>
+        <v>-2.6773</v>
       </c>
       <c r="O9" t="n">
-        <v>0.549</v>
+        <v>0.4246</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7929</v>
+        <v>0.7929</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1893</v>
+        <v>3.7662</v>
       </c>
       <c r="S9" t="n">
-        <v>0.431</v>
+        <v>2.5017</v>
       </c>
       <c r="T9" t="n">
-        <v>0.525</v>
+        <v>1.7971</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.094</v>
+        <v>0.7046</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.0663</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BUZZO</t>
+          <t>F. LASCORZ RIVARES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0911</v>
+        <v>0.2305</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6534</v>
+        <v>-1.3982</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7445000000000001</v>
+        <v>1.6286</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.0661</v>
+        <v>0.5819</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.9399</v>
+        <v>-0.0876</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1262</v>
+        <v>0.6695</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8134</v>
+        <v>0.1609</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2626</v>
+        <v>0.0404</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5508</v>
+        <v>0.1205</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2527</v>
+        <v>0.421</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.6773</v>
+        <v>-0.128</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4246</v>
+        <v>0.549</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7929</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R10" t="n">
-        <v>3.7662</v>
+        <v>1.1893</v>
       </c>
       <c r="S10" t="n">
-        <v>2.298</v>
+        <v>0.4414</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5934</v>
+        <v>0.4232</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7046</v>
+        <v>0.0183</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0663</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9465</v>
+        <v>-0.4061</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0977</v>
+        <v>-2.2204</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1512</v>
+        <v>1.8143</v>
       </c>
       <c r="G11" t="n">
         <v>-0.898</v>
@@ -1312,13 +1312,13 @@
         <v>3.3698</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5373</v>
+        <v>2.0777</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8408</v>
+        <v>1.7182</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6965</v>
+        <v>0.3596</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6505</v>
+        <v>-0.6879</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2732</v>
+        <v>-1.2545</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6228</v>
+        <v>0.5666</v>
       </c>
       <c r="G12" t="n">
         <v>-2.057</v>
@@ -1390,13 +1390,13 @@
         <v>2.3787</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1109</v>
+        <v>0.8517</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.08069999999999999</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0302</v>
+        <v>-0.0864</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8701</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.6749</v>
+        <v>-3.8609</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.6883</v>
+        <v>-5.0147</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0134</v>
+        <v>1.1538</v>
       </c>
       <c r="G13" t="n">
         <v>-6.9247</v>
@@ -1468,13 +1468,13 @@
         <v>2.5769</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9306</v>
+        <v>1.7446</v>
       </c>
       <c r="T13" t="n">
-        <v>0.716</v>
+        <v>1.3896</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2146</v>
+        <v>0.355</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2666</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.7215</v>
+        <v>15.0336</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4291</v>
+        <v>5.740900000000003</v>
       </c>
       <c r="F14" t="n">
-        <v>9.2926</v>
+        <v>9.292600000000002</v>
       </c>
       <c r="G14" t="n">
         <v>-1.5381</v>
@@ -1546,19 +1546,19 @@
         <v>22.7955</v>
       </c>
       <c r="S14" t="n">
-        <v>12.8482</v>
+        <v>13.1601</v>
       </c>
       <c r="T14" t="n">
-        <v>11.5831</v>
+        <v>11.8952</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2652</v>
+        <v>1.2653</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5441</v>
       </c>
       <c r="W14" t="n">
-        <v>5.7539</v>
+        <v>5.753900000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-7.298100000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6244</v>
+        <v>4.1562</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2501</v>
+        <v>4.0277</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6257</v>
+        <v>0.1285</v>
       </c>
       <c r="G15" t="n">
         <v>2.4765</v>
@@ -1624,13 +1624,13 @@
         <v>3.3698</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4468</v>
+        <v>-0.915</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2814</v>
+        <v>0.0589</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.7282</v>
+        <v>-0.974</v>
       </c>
       <c r="V15" t="n">
         <v>1.2071</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8956</v>
+        <v>2.1437</v>
       </c>
       <c r="E16" t="n">
         <v>1.4898</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4057</v>
+        <v>0.6539</v>
       </c>
       <c r="G16" t="n">
         <v>0.8632</v>
@@ -1702,13 +1702,13 @@
         <v>0.5947</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7694</v>
+        <v>-0.5212</v>
       </c>
       <c r="T16" t="n">
         <v>0.2423</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0117</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>1.2071</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0591</v>
+        <v>0.9527</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1267</v>
+        <v>-0.3827</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9325</v>
+        <v>1.3354</v>
       </c>
       <c r="G17" t="n">
         <v>1.9639</v>
@@ -1780,13 +1780,13 @@
         <v>2.7751</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5855</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2975</v>
+        <v>-0.2118</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.883</v>
+        <v>-0.4801</v>
       </c>
       <c r="V17" t="n">
         <v>0.8701</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4672</v>
+        <v>0.0983</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7588</v>
+        <v>-1.6569</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2916</v>
+        <v>1.7552</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8386</v>
@@ -2014,13 +2014,13 @@
         <v>0.9911</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0271</v>
+        <v>-0.4616</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5616</v>
+        <v>-0.4597</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4655</v>
+        <v>-0.0019</v>
       </c>
       <c r="V20" t="n">
         <v>0.4074</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. DOMINGOS</t>
+          <t>F. DAYER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6851</v>
+        <v>-0.9065</v>
       </c>
       <c r="E21" t="n">
-        <v>0.349</v>
+        <v>-0.6461</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0341</v>
+        <v>-0.2603</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.991</v>
+        <v>2.2852</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3942</v>
+        <v>5.2008</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3852</v>
+        <v>-2.9156</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0067</v>
+        <v>2.7437</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0871</v>
+        <v>4.2108</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0804</v>
+        <v>-1.4671</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9843</v>
+        <v>-0.4584</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4813</v>
+        <v>0.99</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4656</v>
+        <v>-1.4485</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5858</v>
+        <v>0.1982</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3964</v>
+        <v>3.1716</v>
       </c>
       <c r="S21" t="n">
-        <v>1.6251</v>
+        <v>-1.9162</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5382</v>
+        <v>-0.4164</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08690000000000001</v>
+        <v>-1.4998</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2666</v>
+        <v>-1.4737</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7997</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5331</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. DAYER</t>
+          <t>K. DOMINGOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2455</v>
+        <v>-1.7541</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6648</v>
+        <v>-0.7716</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5807</v>
+        <v>-0.9825</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2852</v>
+        <v>-0.991</v>
       </c>
       <c r="H22" t="n">
-        <v>5.2008</v>
+        <v>0.3942</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.9156</v>
+        <v>-1.3852</v>
       </c>
       <c r="J22" t="n">
-        <v>2.7437</v>
+        <v>-0.0067</v>
       </c>
       <c r="K22" t="n">
-        <v>4.2108</v>
+        <v>-0.0871</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4671</v>
+        <v>0.0804</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4584</v>
+        <v>-0.9843</v>
       </c>
       <c r="N22" t="n">
-        <v>0.99</v>
+        <v>0.4813</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4485</v>
+        <v>-1.4656</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1982</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R22" t="n">
-        <v>3.1716</v>
+        <v>0.3964</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.2553</v>
+        <v>0.5561</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4351</v>
+        <v>0.4176</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.8201</v>
+        <v>0.1385</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4737</v>
+        <v>0.2666</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.7997</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4737</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0158</v>
+        <v>-3.161</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4112</v>
+        <v>-3.2075</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6045</v>
+        <v>0.0465</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5683</v>
@@ -2248,13 +2248,13 @@
         <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5862</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1176</v>
+        <v>0.3213</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.7038</v>
+        <v>-1.0527</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2666</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6758</v>
+        <v>-4.2366</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3792</v>
+        <v>-1.2587</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.2966</v>
+        <v>-2.9779</v>
       </c>
       <c r="G24" t="n">
         <v>0.2572</v>
@@ -2326,13 +2326,13 @@
         <v>2.1805</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.5543</v>
+        <v>-1.115</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3103</v>
+        <v>-0.1898</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2439</v>
+        <v>-0.9253</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6036</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.9498</v>
+        <v>-7.999</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.8967</v>
+        <v>-7.4892</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0531</v>
+        <v>-0.5098</v>
       </c>
       <c r="G25" t="n">
         <v>-3.6484</v>
@@ -2404,13 +2404,13 @@
         <v>2.9733</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.2488</v>
+        <v>-2.298</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.4351</v>
+        <v>-1.0277</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.8137</v>
+        <v>-1.2704</v>
       </c>
       <c r="V25" t="n">
         <v>-0.0704</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-14.7216</v>
+        <v>-9.9678</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.292400000000001</v>
+        <v>-9.2925</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.4291</v>
+        <v>-0.6752</v>
       </c>
       <c r="G26" t="n">
         <v>1.5382</v>
@@ -2482,13 +2482,13 @@
         <v>17.8401</v>
       </c>
       <c r="S26" t="n">
-        <v>-12.8483</v>
+        <v>-8.0943</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.2651</v>
+        <v>-1.2653</v>
       </c>
       <c r="U26" t="n">
-        <v>-11.583</v>
+        <v>-6.8293</v>
       </c>
       <c r="V26" t="n">
         <v>1.544</v>
